--- a/etf_holdings/2026-10-27_00407A_full_holdings.xlsx
+++ b/etf_holdings/2026-10-27_00407A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-27 00:08:17</t>
+          <t>2026-10-27 22:42:58</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -509,25 +509,25 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>-1.45%2385</t>
+          <t>+0.63%2400</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-1.45%</t>
+          <t>+0.63%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>2385</v>
+        <v>2400</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>9.72%830,000</t>
+          <t>9.75%830,000</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>9.72%</t>
+          <t>9.75%</t>
         </is>
       </c>
       <c r="K2" t="n">
@@ -535,7 +535,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>-0.14%</t>
+          <t>+0.06%</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-27 00:08:17</t>
+          <t>2026-10-27 22:42:58</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -570,25 +570,25 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>-1.36%1085</t>
+          <t>-2.3%1060</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-1.36%</t>
+          <t>-2.3%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>1085</v>
+        <v>1060</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>6.38%1,197,000</t>
+          <t>6.21%1,197,000</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>6.38%</t>
+          <t>6.21%</t>
         </is>
       </c>
       <c r="K3" t="n">
@@ -596,7 +596,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>-0.09%</t>
+          <t>-0.14%</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-27 00:08:17</t>
+          <t>2026-10-27 22:42:58</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -631,25 +631,25 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-2.78%3145</t>
+          <t>-0.48%3130</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-2.78%</t>
+          <t>-0.48%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>3145</v>
+        <v>3130</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>5.79%375,000</t>
+          <t>5.75%375,000</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>5.79%</t>
+          <t>5.75%</t>
         </is>
       </c>
       <c r="K4" t="n">
@@ -657,7 +657,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>-0.16%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-27 00:08:17</t>
+          <t>2026-10-27 22:42:58</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -692,25 +692,25 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>+1.6%5070</t>
+          <t>-6.31%4750</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>+1.6%</t>
+          <t>-6.31%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>5070</v>
+        <v>4750</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>5.60%225,000</t>
+          <t>5.23%225,000</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>5.60%</t>
+          <t>5.23%</t>
         </is>
       </c>
       <c r="K5" t="n">
@@ -718,7 +718,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>+0.09%</t>
+          <t>-0.35%</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-27 00:08:17</t>
+          <t>2026-10-27 22:42:58</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -753,25 +753,25 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>-3.14%4010</t>
+          <t>-1.25%3960</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-3.14%</t>
+          <t>-1.25%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>4010</v>
+        <v>3960</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>5.30%269,000</t>
+          <t>5.21%269,000</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>5.30%</t>
+          <t>5.21%</t>
         </is>
       </c>
       <c r="K6" t="n">
@@ -779,7 +779,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>-0.17%</t>
+          <t>-0.06%</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-27 00:08:17</t>
+          <t>2026-10-27 22:42:58</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -814,25 +814,25 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>-5.19%7585</t>
+          <t>-2.04%7430</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-5.19%</t>
+          <t>-2.04%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>7585</v>
+        <v>7430</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>4.77%128,000</t>
+          <t>4.66%128,000</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>4.77%</t>
+          <t>4.66%</t>
         </is>
       </c>
       <c r="K7" t="n">
@@ -840,7 +840,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>-0.25%</t>
+          <t>-0.10%</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-27 00:08:17</t>
+          <t>2026-10-27 22:42:58</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -875,25 +875,25 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>-5.6%1265</t>
+          <t>-0.79%1255</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-5.6%</t>
+          <t>-0.79%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>1265</v>
+        <v>1255</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>3.78%608,000</t>
+          <t>3.74%608,000</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>3.78%</t>
+          <t>3.74%</t>
         </is>
       </c>
       <c r="K8" t="n">
@@ -901,7 +901,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>-0.22%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-27 00:08:17</t>
+          <t>2026-10-27 22:42:58</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -936,25 +936,25 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>-7.12%6070</t>
+          <t>-3.46%5860</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-7.12%</t>
+          <t>-3.46%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>6070</v>
+        <v>5860</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>3.46%116,000</t>
+          <t>3.33%116,000</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>3.46%</t>
+          <t>3.33%</t>
         </is>
       </c>
       <c r="K9" t="n">
@@ -962,7 +962,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>-0.26%</t>
+          <t>-0.12%</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-27 00:08:17</t>
+          <t>2026-10-27 22:42:58</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -997,25 +997,25 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>-4.39%654</t>
+          <t>-0.46%651</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-4.39%</t>
+          <t>-0.46%</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>654</v>
+        <v>651</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>3.06%952,000</t>
+          <t>3.03%952,000</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>3.06%</t>
+          <t>3.03%</t>
         </is>
       </c>
       <c r="K10" t="n">
@@ -1023,7 +1023,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>-0.14%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-27 00:08:17</t>
+          <t>2026-10-27 22:42:58</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1053,38 +1053,38 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>6274台燿</t>
+          <t>1303南亞</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>-5.33%1420</t>
+          <t>-1.16%297.5</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-5.33%</t>
+          <t>-1.16%</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>1420</v>
+        <v>297.5</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2.71%389,000</t>
+          <t>2.61%1,795,000</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2.71%</t>
+          <t>2.61%</t>
         </is>
       </c>
       <c r="K11" t="n">
-        <v>389000</v>
+        <v>1795000</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>-0.15%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-27 00:08:17</t>
+          <t>2026-10-27 22:42:58</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1114,38 +1114,38 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>3665貿聯-KY</t>
+          <t>6669緯穎</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>-3.85%1875</t>
+          <t>+5.98%1950</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-3.85%</t>
+          <t>+5.98%</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>1875</v>
+        <v>1950</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2.56%278,000</t>
+          <t>2.55%267,644</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2.56%</t>
+          <t>2.55%</t>
         </is>
       </c>
       <c r="K12" t="n">
-        <v>278000</v>
+        <v>267644</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>-0.10%</t>
+          <t>+0.14%</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-27 00:08:17</t>
+          <t>2026-10-27 22:42:58</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1180,25 +1180,25 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>-4%1560</t>
+          <t>-3.21%1510</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-4%</t>
+          <t>-3.21%</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>1560</v>
+        <v>1510</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2.47%323,000</t>
+          <t>2.39%323,000</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2.47%</t>
+          <t>2.39%</t>
         </is>
       </c>
       <c r="K13" t="n">
@@ -1206,7 +1206,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>-0.10%</t>
+          <t>-0.08%</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-27 00:08:17</t>
+          <t>2026-10-27 22:42:58</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1236,38 +1236,38 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>6669緯穎</t>
+          <t>3665貿聯-KY</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>-2.13%1840</t>
+          <t>-7.47%1735</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-2.13%</t>
+          <t>-7.47%</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>1840</v>
+        <v>1735</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2.42%267,644</t>
+          <t>2.36%278,000</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2.42%</t>
+          <t>2.36%</t>
         </is>
       </c>
       <c r="K14" t="n">
-        <v>267644</v>
+        <v>278000</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>-0.05%</t>
+          <t>-0.19%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-27 00:08:17</t>
+          <t>2026-10-27 22:42:58</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1297,38 +1297,38 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>6223旺矽</t>
+          <t>2327國巨*</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>-2.3%4890</t>
+          <t>+2.76%521</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-2.3%</t>
+          <t>+2.76%</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>4890</v>
+        <v>521</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2.26%94,000</t>
+          <t>2.28%895,000</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2.26%</t>
+          <t>2.28%</t>
         </is>
       </c>
       <c r="K15" t="n">
-        <v>94000</v>
+        <v>895000</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>-0.05%</t>
+          <t>+0.06%</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-27 00:08:17</t>
+          <t>2026-10-27 22:42:58</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1358,38 +1358,38 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2327國巨*</t>
+          <t>6223旺矽</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>-6.46%507</t>
+          <t>-2.04%4790</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-6.46%</t>
+          <t>-2.04%</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>507</v>
+        <v>4790</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2.23%895,000</t>
+          <t>2.20%94,000</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2.23%</t>
+          <t>2.20%</t>
         </is>
       </c>
       <c r="K16" t="n">
-        <v>895000</v>
+        <v>94000</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>-0.15%</t>
+          <t>-0.05%</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-10-27 00:08:18</t>
+          <t>2026-10-27 22:42:59</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1419,38 +1419,38 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>1303南亞</t>
+          <t>6274台燿</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>-6.08%301</t>
+          <t>-9.86%1280</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-6.08%</t>
+          <t>-9.86%</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>301</v>
+        <v>1280</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2.06%1,395,000</t>
+          <t>1.94%309,000</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2.06%</t>
+          <t>1.94%</t>
         </is>
       </c>
       <c r="K17" t="n">
-        <v>1395000</v>
+        <v>309000</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>-0.13%</t>
+          <t>-0.21%</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-10-27 00:08:18</t>
+          <t>2026-10-27 22:42:59</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1485,16 +1485,16 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>-3.22%9755</t>
+          <t>+0.56%9810</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-3.22%</t>
+          <t>+0.56%</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>9755</v>
+        <v>9810</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -1511,7 +1511,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>-0.06%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-10-27 00:08:18</t>
+          <t>2026-10-27 22:42:59</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1541,38 +1541,38 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2368金像電</t>
+          <t>3081聯亞</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>-6.69%1115</t>
+          <t>+5.26%2500</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-6.69%</t>
+          <t>+5.26%</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>1115</v>
+        <v>2500</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1.68%306,000</t>
+          <t>1.87%153,000</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>1.68%</t>
+          <t>1.87%</t>
         </is>
       </c>
       <c r="K19" t="n">
-        <v>306000</v>
+        <v>153000</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>-0.12%</t>
+          <t>+0.09%</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-10-27 00:08:18</t>
+          <t>2026-10-27 22:42:59</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1602,38 +1602,38 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>3008大立光</t>
+          <t>2368金像電</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>+0.08%6175</t>
+          <t>-3.14%1080</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>+0.08%</t>
+          <t>-3.14%</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>6175</v>
+        <v>1080</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1.58%52,000</t>
+          <t>1.62%306,000</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>1.58%</t>
+          <t>1.62%</t>
         </is>
       </c>
       <c r="K20" t="n">
-        <v>52000</v>
+        <v>306000</v>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.05%</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-10-27 00:08:18</t>
+          <t>2026-10-27 22:42:59</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1668,25 +1668,25 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>-5.26%1260</t>
+          <t>+1.98%1285</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-5.26%</t>
+          <t>+1.98%</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>1260</v>
+        <v>1285</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1.58%255,000</t>
+          <t>1.60%255,000</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>1.58%</t>
+          <t>1.60%</t>
         </is>
       </c>
       <c r="K21" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>-0.09%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-10-27 00:08:18</t>
+          <t>2026-10-27 22:42:59</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1729,25 +1729,25 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>-2.2%1775</t>
+          <t>-0.85%1760</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-2.2%</t>
+          <t>-0.85%</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>1775</v>
+        <v>1760</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1.57%180,000</t>
+          <t>1.55%180,000</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>1.57%</t>
+          <t>1.55%</t>
         </is>
       </c>
       <c r="K22" t="n">
@@ -1755,7 +1755,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-10-27 00:08:18</t>
+          <t>2026-10-27 22:42:59</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1785,34 +1785,34 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2301光寶科</t>
+          <t>3008大立光</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>-3.04%255.5</t>
+          <t>-2.83%6000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-3.04%</t>
+          <t>-2.83%</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>255.5</v>
+        <v>6000</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>1.46%1,160,000</t>
+          <t>1.53%52,000</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>1.46%</t>
+          <t>1.53%</t>
         </is>
       </c>
       <c r="K23" t="n">
-        <v>1160000</v>
+        <v>52000</v>
       </c>
       <c r="L23" t="inlineStr">
         <is>
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-10-27 00:08:18</t>
+          <t>2026-10-27 22:42:59</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1846,25 +1846,25 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>6510精測</t>
+          <t>2301光寶科</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>-5.11%3065</t>
+          <t>-1.17%252.5</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-5.11%</t>
+          <t>-1.17%</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>3065</v>
+        <v>252.5</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>1.43%95,000</t>
+          <t>1.43%1,160,000</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -1873,11 +1873,11 @@
         </is>
       </c>
       <c r="K24" t="n">
-        <v>95000</v>
+        <v>1160000</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>-0.07%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-10-27 00:08:18</t>
+          <t>2026-10-27 22:42:59</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1907,38 +1907,38 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>8996高力</t>
+          <t>6510精測</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>-6.02%1560</t>
+          <t>-5.06%2910</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-6.02%</t>
+          <t>-5.06%</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>1560</v>
+        <v>2910</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>1.37%179,000</t>
+          <t>1.35%95,000</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>1.37%</t>
+          <t>1.35%</t>
         </is>
       </c>
       <c r="K25" t="n">
-        <v>179000</v>
+        <v>95000</v>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>-0.09%</t>
+          <t>-0.07%</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-10-27 00:08:18</t>
+          <t>2026-10-27 22:42:59</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1973,25 +1973,25 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>-3.06%16010</t>
+          <t>+0.03%16015</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-3.06%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>16010</v>
+        <v>16015</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>1.33%16,900</t>
+          <t>1.32%16,900</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>1.33%</t>
+          <t>1.32%</t>
         </is>
       </c>
       <c r="K26" t="n">
@@ -1999,7 +1999,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-10-27 00:08:18</t>
+          <t>2026-10-27 22:42:59</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2029,38 +2029,38 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>3081聯亞</t>
+          <t>8996高力</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>-9.52%2375</t>
+          <t>-6.09%1465</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-9.52%</t>
+          <t>-6.09%</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>2375</v>
+        <v>1465</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>1.32%113,000</t>
+          <t>1.28%179,000</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>1.32%</t>
+          <t>1.28%</t>
         </is>
       </c>
       <c r="K27" t="n">
-        <v>113000</v>
+        <v>179000</v>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>-0.13%</t>
+          <t>-0.08%</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-10-27 00:08:18</t>
+          <t>2026-10-27 22:42:59</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2095,25 +2095,25 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>-2.51%2335</t>
+          <t>-3.64%2250</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-2.51%</t>
+          <t>-3.64%</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>2335</v>
+        <v>2250</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>1.28%112,000</t>
+          <t>1.23%112,000</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>1.28%</t>
+          <t>1.23%</t>
         </is>
       </c>
       <c r="K28" t="n">
@@ -2121,7 +2121,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>-0.05%</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-10-27 00:08:18</t>
+          <t>2026-10-27 22:42:59</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2151,38 +2151,38 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>4958臻鼎-KY</t>
+          <t>3231緯創</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>-1.9%567</t>
+          <t>+0.26%190.5</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-1.9%</t>
+          <t>+0.26%</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>567</v>
+        <v>190.5</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>1.16%418,000</t>
+          <t>1.12%1,198,000</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>1.16%</t>
+          <t>1.12%</t>
         </is>
       </c>
       <c r="K29" t="n">
-        <v>418000</v>
+        <v>1198000</v>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-10-27 00:08:18</t>
+          <t>2026-10-27 22:42:59</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2212,38 +2212,38 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>3231緯創</t>
+          <t>4958臻鼎-KY</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>-2.56%190</t>
+          <t>-8.29%520</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>-2.56%</t>
+          <t>-8.29%</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>190</v>
+        <v>520</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>1.12%1,198,000</t>
+          <t>1.06%418,000</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>1.12%</t>
+          <t>1.06%</t>
         </is>
       </c>
       <c r="K30" t="n">
-        <v>1198000</v>
+        <v>418000</v>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>-0.09%</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-10-27 00:08:18</t>
+          <t>2026-10-27 22:42:59</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2278,25 +2278,25 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>+2.58%119.5</t>
+          <t>-2.51%116.5</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>+2.58%</t>
+          <t>-2.51%</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>119.5</v>
+        <v>116.5</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>1.09%1,850,000</t>
+          <t>1.05%1,850,000</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>1.09%</t>
+          <t>1.05%</t>
         </is>
       </c>
       <c r="K31" t="n">
@@ -2304,7 +2304,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-10-27 00:08:20</t>
+          <t>2026-10-27 22:43:00</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2339,25 +2339,25 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>-1.49%1980</t>
+          <t>-1.26%1955</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>-1.49%</t>
+          <t>-1.26%</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>1980</v>
+        <v>1955</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>1.02%105,000</t>
+          <t>1.00%105,000</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>1.02%</t>
+          <t>1.00%</t>
         </is>
       </c>
       <c r="K32" t="n">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-10-27 00:08:20</t>
+          <t>2026-10-27 22:43:00</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2400,25 +2400,25 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>-3.53%846</t>
+          <t>-1.65%832</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>-3.53%</t>
+          <t>-1.65%</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>846</v>
+        <v>832</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>1.01%243,000</t>
+          <t>0.99%243,000</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>1.01%</t>
+          <t>0.99%</t>
         </is>
       </c>
       <c r="K33" t="n">
@@ -2426,7 +2426,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-10-27 00:08:20</t>
+          <t>2026-10-27 22:43:00</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2456,38 +2456,38 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>3491昇達科</t>
+          <t>3533嘉澤</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>-7.69%1320</t>
+          <t>+7.24%1925</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>-7.69%</t>
+          <t>+7.24%</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>1320</v>
+        <v>1925</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.88%135,000</t>
+          <t>0.98%104,000</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0.88%</t>
+          <t>0.98%</t>
         </is>
       </c>
       <c r="K34" t="n">
-        <v>135000</v>
+        <v>104000</v>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>-0.07%</t>
+          <t>+0.07%</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-10-27 00:08:20</t>
+          <t>2026-10-27 22:43:00</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2522,25 +2522,25 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>-5.15%414</t>
+          <t>+6.52%441</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>-5.15%</t>
+          <t>+6.52%</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>414</v>
+        <v>441</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>0.87%426,000</t>
+          <t>0.92%426,000</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>0.87%</t>
+          <t>0.92%</t>
         </is>
       </c>
       <c r="K35" t="n">
@@ -2548,7 +2548,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>-0.05%</t>
+          <t>+0.06%</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-10-27 00:08:20</t>
+          <t>2026-10-27 22:43:00</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2583,25 +2583,25 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>-1.19%583</t>
+          <t>+2.74%599</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-1.19%</t>
+          <t>+2.74%</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>583</v>
+        <v>599</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>0.86%302,000</t>
+          <t>0.89%302,000</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>0.86%</t>
+          <t>0.89%</t>
         </is>
       </c>
       <c r="K36" t="n">
@@ -2609,7 +2609,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-10-27 00:08:20</t>
+          <t>2026-10-27 22:43:00</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2639,38 +2639,38 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>3131弘塑</t>
+          <t>3491昇達科</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>-5.48%1985</t>
+          <t>-3.41%1275</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>-5.48%</t>
+          <t>-3.41%</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>1985</v>
+        <v>1275</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>0.78%80,000</t>
+          <t>0.84%135,000</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>0.78%</t>
+          <t>0.84%</t>
         </is>
       </c>
       <c r="K37" t="n">
-        <v>80000</v>
+        <v>135000</v>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-10-27 00:08:20</t>
+          <t>2026-10-27 22:43:00</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2700,38 +2700,38 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>3293鈊象</t>
+          <t>3131弘塑</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>+0.64%787</t>
+          <t>+1.51%2015</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>+0.64%</t>
+          <t>+1.51%</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>787</v>
+        <v>2015</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>0.66%171,000</t>
+          <t>0.79%80,000</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>0.66%</t>
+          <t>0.79%</t>
         </is>
       </c>
       <c r="K38" t="n">
-        <v>171000</v>
+        <v>80000</v>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-10-27 00:08:20</t>
+          <t>2026-10-27 22:43:00</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2761,38 +2761,38 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2303聯電</t>
+          <t>3293鈊象</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>-1.95%125.5</t>
+          <t>+1.14%796</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>-1.95%</t>
+          <t>+1.14%</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>125.5</v>
+        <v>796</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>0.54%878,000</t>
+          <t>0.67%171,000</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>0.54%</t>
+          <t>0.67%</t>
         </is>
       </c>
       <c r="K39" t="n">
-        <v>878000</v>
+        <v>171000</v>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-10-27 00:08:20</t>
+          <t>2026-10-27 22:43:00</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2822,34 +2822,34 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>3533嘉澤</t>
+          <t>2303聯電</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>-1.37%1795</t>
+          <t>-2.39%122.5</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>-1.37%</t>
+          <t>-2.39%</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>1795</v>
+        <v>122.5</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>0.48%54,000</t>
+          <t>0.53%878,000</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>0.48%</t>
+          <t>0.53%</t>
         </is>
       </c>
       <c r="K40" t="n">
-        <v>54000</v>
+        <v>878000</v>
       </c>
       <c r="L40" t="inlineStr">
         <is>
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-10-27 00:08:20</t>
+          <t>2026-10-27 22:43:00</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2888,25 +2888,25 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>-6.65%224.5</t>
+          <t>-3.79%216</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>-6.65%</t>
+          <t>-3.79%</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>224.5</v>
+        <v>216</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>0.44%400,000</t>
+          <t>0.42%400,000</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>0.44%</t>
+          <t>0.42%</t>
         </is>
       </c>
       <c r="K41" t="n">
@@ -2914,7 +2914,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-10-27 00:08:20</t>
+          <t>2026-10-27 22:43:00</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2949,25 +2949,25 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>+0.36%275</t>
+          <t>+2.36%281.5</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>+0.36%</t>
+          <t>+2.36%</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>275</v>
+        <v>281.5</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>0.34%252,000</t>
+          <t>0.35%252,000</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>0.34%</t>
+          <t>0.35%</t>
         </is>
       </c>
       <c r="K42" t="n">
@@ -2975,7 +2975,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-10-27 00:08:20</t>
+          <t>2026-10-27 22:43:00</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3010,16 +3010,16 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>-1.28%1160</t>
+          <t>+2.59%1190</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>-1.28%</t>
+          <t>+2.59%</t>
         </is>
       </c>
       <c r="H43" t="n">
-        <v>1160</v>
+        <v>1190</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
@@ -3036,7 +3036,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-10-27 00:08:20</t>
+          <t>2026-10-27 22:43:00</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3071,25 +3071,25 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>-2.59%1880</t>
+          <t>+1.6%1910</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>-2.59%</t>
+          <t>+1.6%</t>
         </is>
       </c>
       <c r="H44" t="n">
-        <v>1880</v>
+        <v>1910</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>0.31%34,000</t>
+          <t>0.32%34,000</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>0.31%</t>
+          <t>0.32%</t>
         </is>
       </c>
       <c r="K44" t="n">
@@ -3097,7 +3097,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-10-27 00:08:20</t>
+          <t>2026-10-27 22:43:00</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3132,25 +3132,25 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>-4.33%795</t>
+          <t>+2.39%814</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>-4.33%</t>
+          <t>+2.39%</t>
         </is>
       </c>
       <c r="H45" t="n">
-        <v>795</v>
+        <v>814</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>0.30%77,000</t>
+          <t>0.31%77,000</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.31%</t>
         </is>
       </c>
       <c r="K45" t="n">
@@ -3158,7 +3158,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-10-27 00:08:20</t>
+          <t>2026-10-27 22:43:00</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3193,25 +3193,25 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>-1.35%328</t>
+          <t>+0.76%330.5</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>-1.35%</t>
+          <t>+0.76%</t>
         </is>
       </c>
       <c r="H46" t="n">
-        <v>328</v>
+        <v>330.5</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>0.28%176,828</t>
+          <t>0.29%176,828</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>0.28%</t>
+          <t>0.29%</t>
         </is>
       </c>
       <c r="K46" t="n">
@@ -3219,7 +3219,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-10-27 00:08:21</t>
+          <t>2026-10-27 22:43:02</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3254,25 +3254,25 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>-2.53%772</t>
+          <t>+2.72%793</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>-2.53%</t>
+          <t>+2.72%</t>
         </is>
       </c>
       <c r="H47" t="n">
-        <v>772</v>
+        <v>793</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>0.26%69,000</t>
+          <t>0.27%69,000</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>0.26%</t>
+          <t>0.27%</t>
         </is>
       </c>
       <c r="K47" t="n">
@@ -3280,7 +3280,7 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-10-27 00:08:21</t>
+          <t>2026-10-27 22:43:02</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3315,16 +3315,16 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>-4.05%2485</t>
+          <t>+1.21%2515</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>-4.05%</t>
+          <t>+1.21%</t>
         </is>
       </c>
       <c r="H48" t="n">
-        <v>2485</v>
+        <v>2515</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
@@ -3341,7 +3341,7 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-10-27 00:08:21</t>
+          <t>2026-10-27 22:43:02</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3376,16 +3376,16 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>-4.01%550</t>
+          <t>-0.73%546</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>-4.01%</t>
+          <t>-0.73%</t>
         </is>
       </c>
       <c r="H49" t="n">
-        <v>550</v>
+        <v>546</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
@@ -3402,7 +3402,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-10-27 00:08:21</t>
+          <t>2026-10-27 22:43:02</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3437,25 +3437,25 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>-3.13%154.5</t>
+          <t>+5.5%163</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>-3.13%</t>
+          <t>+5.5%</t>
         </is>
       </c>
       <c r="H50" t="n">
-        <v>154.5</v>
+        <v>163</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>0.14%187,000</t>
+          <t>0.15%187,000</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>0.14%</t>
+          <t>0.15%</t>
         </is>
       </c>
       <c r="K50" t="n">
@@ -3463,7 +3463,7 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-10-27 00:08:21</t>
+          <t>2026-10-27 22:43:02</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3498,16 +3498,16 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>-1.79%1100</t>
+          <t>+3.64%1140</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>-1.79%</t>
+          <t>+3.64%</t>
         </is>
       </c>
       <c r="H51" t="n">
-        <v>1100</v>
+        <v>1140</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
@@ -3524,7 +3524,7 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">

--- a/etf_holdings/2026-10-27_00407A_full_holdings.xlsx
+++ b/etf_holdings/2026-10-27_00407A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-27 22:42:58</t>
+          <t>2026-10-27 22:55:28</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-27 22:42:58</t>
+          <t>2026-10-27 22:55:28</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-27 22:42:58</t>
+          <t>2026-10-27 22:55:28</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-27 22:42:58</t>
+          <t>2026-10-27 22:55:28</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-27 22:42:58</t>
+          <t>2026-10-27 22:55:28</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-27 22:42:58</t>
+          <t>2026-10-27 22:55:28</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-27 22:42:58</t>
+          <t>2026-10-27 22:55:28</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-27 22:42:58</t>
+          <t>2026-10-27 22:55:28</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-27 22:42:58</t>
+          <t>2026-10-27 22:55:28</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-27 22:42:58</t>
+          <t>2026-10-27 22:55:28</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-27 22:42:58</t>
+          <t>2026-10-27 22:55:28</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-27 22:42:58</t>
+          <t>2026-10-27 22:55:28</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-27 22:42:58</t>
+          <t>2026-10-27 22:55:28</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-27 22:42:58</t>
+          <t>2026-10-27 22:55:28</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-27 22:42:58</t>
+          <t>2026-10-27 22:55:28</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-10-27 22:42:59</t>
+          <t>2026-10-27 22:55:30</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-10-27 22:42:59</t>
+          <t>2026-10-27 22:55:30</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-10-27 22:42:59</t>
+          <t>2026-10-27 22:55:30</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-10-27 22:42:59</t>
+          <t>2026-10-27 22:55:30</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-10-27 22:42:59</t>
+          <t>2026-10-27 22:55:30</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-10-27 22:42:59</t>
+          <t>2026-10-27 22:55:30</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-10-27 22:42:59</t>
+          <t>2026-10-27 22:55:30</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-10-27 22:42:59</t>
+          <t>2026-10-27 22:55:30</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-10-27 22:42:59</t>
+          <t>2026-10-27 22:55:30</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-10-27 22:42:59</t>
+          <t>2026-10-27 22:55:30</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-10-27 22:42:59</t>
+          <t>2026-10-27 22:55:30</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-10-27 22:42:59</t>
+          <t>2026-10-27 22:55:30</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-10-27 22:42:59</t>
+          <t>2026-10-27 22:55:30</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-10-27 22:42:59</t>
+          <t>2026-10-27 22:55:30</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-10-27 22:42:59</t>
+          <t>2026-10-27 22:55:30</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-10-27 22:43:00</t>
+          <t>2026-10-27 22:55:31</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-10-27 22:43:00</t>
+          <t>2026-10-27 22:55:31</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-10-27 22:43:00</t>
+          <t>2026-10-27 22:55:31</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-10-27 22:43:00</t>
+          <t>2026-10-27 22:55:31</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-10-27 22:43:00</t>
+          <t>2026-10-27 22:55:31</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-10-27 22:43:00</t>
+          <t>2026-10-27 22:55:31</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-10-27 22:43:00</t>
+          <t>2026-10-27 22:55:31</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-10-27 22:43:00</t>
+          <t>2026-10-27 22:55:31</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-10-27 22:43:00</t>
+          <t>2026-10-27 22:55:31</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-10-27 22:43:00</t>
+          <t>2026-10-27 22:55:31</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-10-27 22:43:00</t>
+          <t>2026-10-27 22:55:31</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-10-27 22:43:00</t>
+          <t>2026-10-27 22:55:31</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-10-27 22:43:00</t>
+          <t>2026-10-27 22:55:31</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-10-27 22:43:00</t>
+          <t>2026-10-27 22:55:31</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-10-27 22:43:00</t>
+          <t>2026-10-27 22:55:31</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-10-27 22:43:02</t>
+          <t>2026-10-27 22:55:32</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-10-27 22:43:02</t>
+          <t>2026-10-27 22:55:32</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-10-27 22:43:02</t>
+          <t>2026-10-27 22:55:32</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-10-27 22:43:02</t>
+          <t>2026-10-27 22:55:32</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-10-27 22:43:02</t>
+          <t>2026-10-27 22:55:32</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
